--- a/demo/series/musterwerk-complete/stueckliste.xlsx
+++ b/demo/series/musterwerk-complete/stueckliste.xlsx
@@ -5,12 +5,17 @@
     <sheet name="Stammdaten" sheetId="1" r:id="rId1"/>
     <sheet name="Stückliste" sheetId="2" r:id="rId2"/>
     <sheet name="Leistung" sheetId="3" r:id="rId3"/>
+    <sheet name="Materialdeklaration" sheetId="4" r:id="rId4"/>
+    <sheet name="Gefahrstoffe" sheetId="5" r:id="rId5"/>
+    <sheet name="Ersatzteile" sheetId="6" r:id="rId6"/>
+    <sheet name="Bezugsquellen" sheetId="7" r:id="rId7"/>
+    <sheet name="BMS-Auslesung" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Batteriepass-ID</t>
   </si>
@@ -81,6 +86,9 @@
     <t>Innenwiderstand Pack</t>
   </si>
   <si>
+    <t>Innenwiderstand Zelle</t>
+  </si>
+  <si>
     <t>Anfänglicher Round-Trip-Wirkungsgrad</t>
   </si>
   <si>
@@ -97,6 +105,90 @@
   </si>
   <si>
     <t>Erschöpfungsschwelle</t>
+  </si>
+  <si>
+    <t>Komponente</t>
+  </si>
+  <si>
+    <t>Kritischer Rohstoff</t>
+  </si>
+  <si>
+    <t>Lithium</t>
+  </si>
+  <si>
+    <t>Cobalt</t>
+  </si>
+  <si>
+    <t>Natural graphite</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Lithium hexafluorophosphate</t>
+  </si>
+  <si>
+    <t>Stoff</t>
+  </si>
+  <si>
+    <t>Gefahrenklasse</t>
+  </si>
+  <si>
+    <t>Konzentration [%]</t>
+  </si>
+  <si>
+    <t>Gefahrenhinweise</t>
+  </si>
+  <si>
+    <t>Teilenummer</t>
+  </si>
+  <si>
+    <t>Bezugsquelle</t>
+  </si>
+  <si>
+    <t>Battery management system</t>
+  </si>
+  <si>
+    <t>Battery module</t>
+  </si>
+  <si>
+    <t>Cooling plate</t>
+  </si>
+  <si>
+    <t>Lieferant</t>
+  </si>
+  <si>
+    <t>Straße</t>
+  </si>
+  <si>
+    <t>PLZ</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>E-Mail</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>Musterwerk Ersatzteile GmbH</t>
+  </si>
+  <si>
+    <t>Zeitstempel</t>
+  </si>
+  <si>
+    <t>State of Certified Energy (SOCE)</t>
+  </si>
+  <si>
+    <t>Ladezustand (SoC)</t>
+  </si>
+  <si>
+    <t>Anzahl Vollzyklen</t>
+  </si>
+  <si>
+    <t>Batterietemperatur</t>
   </si>
 </sst>
 </file>
@@ -226,7 +318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>siehe Materialdeklaration</t>
         </is>
       </c>
       <c r="C2">
@@ -343,11 +435,11 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>96</v>
+        <v>0.0012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Ohm</t>
         </is>
       </c>
     </row>
@@ -356,7 +448,7 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -369,11 +461,11 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -382,11 +474,11 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jahre</t>
+          <t>kW</t>
         </is>
       </c>
     </row>
@@ -395,11 +487,11 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>0.5</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Jahre</t>
         </is>
       </c>
     </row>
@@ -408,11 +500,435 @@
         <v>28</v>
       </c>
       <c r="B11">
+        <v>0.5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12">
         <v>70</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7439-93-2</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>6.4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cathode</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7440-48-4</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>4.1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cathode</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7782-42-5</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>38</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Anode</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7440-50-8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Anode</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21324-40-3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Electrolyte</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>21324-40-3</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AcuteToxicity</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>1.2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Electrolyte</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>H301 Toxic if swallowed; H314 Causes severe skin burns and eye damage</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MW-BMS-7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Musterwerk Batteriesysteme GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MW-MOD-48-A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Musterwerk Ersatzteile GmbH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MW-CP-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Musterwerk Ersatzteile GmbH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Werkstrasse 2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>28199</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ersatzteile@musterwerk.example</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://ersatzteile.musterwerk.example</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2">
+        <v>99.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-31T06:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3">
+        <v>70</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-31T06:00:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Zyklen</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-30T18:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5">
+        <v>23.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-31T06:00:00Z</t>
         </is>
       </c>
     </row>
